--- a/resources/templates/standard/L1100-19.xlsx
+++ b/resources/templates/standard/L1100-19.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>전달 교육 보고서</t>
   </si>
@@ -773,11 +776,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -887,7 +892,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -897,7 +902,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="7" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -907,7 +912,7 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
       <c r="Q4" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
@@ -930,7 +935,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -940,7 +945,7 @@
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
       <c r="I5" s="11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J5" s="11"/>
       <c r="K5" s="11"/>
@@ -950,7 +955,7 @@
       <c r="O5" s="12"/>
       <c r="P5" s="12"/>
       <c r="Q5" s="11" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R5" s="11"/>
       <c r="S5" s="11"/>
@@ -973,7 +978,7 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
@@ -1012,7 +1017,7 @@
     </row>
     <row r="7" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -1051,39 +1056,39 @@
     </row>
     <row r="8" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
       <c r="D8" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
       <c r="K8" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" s="11"/>
       <c r="M8" s="11"/>
       <c r="N8" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O8" s="11"/>
       <c r="P8" s="11"/>
       <c r="Q8" s="11"/>
       <c r="R8" s="11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="S8" s="11"/>
       <c r="T8" s="11"/>
       <c r="U8" s="11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
@@ -1243,24 +1248,24 @@
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
       <c r="AE12" s="19" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF12" s="20" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG12" s="20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH12" s="20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI12" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="21"/>
       <c r="C13" s="21"/>
@@ -1780,7 +1785,7 @@
     </row>
     <row r="27" ht="20.15" customHeight="1" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B27" s="26"/>
       <c r="C27" s="26"/>
